--- a/reports.xlsx
+++ b/reports.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="11_F25DC773A252ABDACC104865891F55C05BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EA0DD79-DD88-4A55-82BF-4EDA7D8C8335}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_F25DC773A252ABDACC104865891F55C05BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CFA76B5-7221-47A6-B313-2B5E8947BB62}"/>
   <bookViews>
-    <workbookView xWindow="12900" yWindow="3240" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$E$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Avantis US</t>
   </si>
@@ -60,12 +60,6 @@
     <t>iShares Core MSCI Pacific ex-Japan UCITS ETF</t>
   </si>
   <si>
-    <t>iShares II PLC</t>
-  </si>
-  <si>
-    <t>iShares MSCI World Islamic UCITS ETF</t>
-  </si>
-  <si>
     <t>iShares IV plc</t>
   </si>
   <si>
@@ -90,9 +84,6 @@
     <t>IWDA, IEMS, WSML, IEMA</t>
   </si>
   <si>
-    <t>iShares US</t>
-  </si>
-  <si>
     <t>JPMorgan</t>
   </si>
   <si>
@@ -111,9 +102,6 @@
     <t>SPDR-II</t>
   </si>
   <si>
-    <t xml:space="preserve"> SPDR MSCI</t>
-  </si>
-  <si>
     <t>Small cap value</t>
   </si>
   <si>
@@ -148,13 +136,31 @@
   </si>
   <si>
     <t>SSAC</t>
+  </si>
+  <si>
+    <t>SPDR MSCI All Country World</t>
+  </si>
+  <si>
+    <t>Cardano ESG Transition Enhanced Index Equity Global</t>
+  </si>
+  <si>
+    <t>GOLDMAN SACHS ENHANCED INDEX SUSTAINABLE EQUITY FUND A (NL)</t>
+  </si>
+  <si>
+    <t>https://www.northerntrust.com/netherlands/what-we-do/investment-management/pooled-funds</t>
+  </si>
+  <si>
+    <t>World A + I, EM A en G. Master zie link.</t>
+  </si>
+  <si>
+    <t>Opmerkingen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +172,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -188,10 +202,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -201,8 +216,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -216,6 +233,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:E28"/>
+  <dimension ref="B1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -491,263 +512,261 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1">
-        <v>45260</v>
+        <v>45383</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="C3" s="1">
-        <v>45291</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1">
-        <v>45323</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1">
-        <v>45382</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>45382</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
+        <v>45596</v>
+      </c>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1">
-        <v>45383</v>
+        <v>45626</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1">
-        <v>45383</v>
+        <v>45626</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="1">
-        <v>45383</v>
+        <v>18</v>
+      </c>
+      <c r="C9" s="4">
+        <v>45657</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1">
-        <v>45383</v>
+        <v>45657</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1">
-        <v>45383</v>
+        <v>45657</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1">
-        <v>45383</v>
+        <v>45689</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="4">
-        <v>45400</v>
+        <v>22</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45747</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="3" t="s">
-        <v>12</v>
+      <c r="B14" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="1">
-        <v>45413</v>
+        <v>45747</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2"/>
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C15" s="1">
-        <v>45444</v>
+        <v>45748</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1">
-        <v>45473</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>45748</v>
+      </c>
+      <c r="D17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="1">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45778</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="1">
+        <v>45809</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="1">
-        <v>45473</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="C22" s="1">
+        <v>45838</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45838</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="1">
-        <v>45474</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C24" s="1">
+        <v>45839</v>
+      </c>
+      <c r="D24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1">
-        <v>45535</v>
-      </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>45535</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="1">
-        <v>45596</v>
-      </c>
-      <c r="D21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="1">
-        <v>45596</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="1">
-        <v>45596</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="1">
-        <v>45596</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="1">
-        <v>45626</v>
-      </c>
-      <c r="D25" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
         <v>32</v>
       </c>
-      <c r="C26" s="1">
-        <v>45657</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:D1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D28">
+  <autoFilter ref="B1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E26">
       <sortCondition ref="C1"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="E17" r:id="rId1" xr:uid="{16634FF5-BB58-4C5E-8512-A7A665D7C792}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/reports.xlsx
+++ b/reports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7c741cee80ec8cf3/Financieel/IndexFondsenOnderzoek/KeuzeWelkIndexFonds/OnderzoekPerFonds/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_F25DC773A252ABDACC104865891F55C05BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CFA76B5-7221-47A6-B313-2B5E8947BB62}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="11_F25DC773A252ABDACC104865891F55C05BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0AAFB81-9FB8-4DE5-BF37-737C927F34BE}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Avantis US</t>
   </si>
@@ -124,12 +124,6 @@
   </si>
   <si>
     <t>Amundi WEBG</t>
-  </si>
-  <si>
-    <t>21-05-2025?</t>
-  </si>
-  <si>
-    <t>31-12-2025?</t>
   </si>
   <si>
     <t>iShares V PLC</t>
@@ -233,10 +227,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -521,241 +511,241 @@
         <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
-        <v>45383</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
+        <v>45626</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C3" s="1">
-        <v>45535</v>
+        <v>45626</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
-        <v>45596</v>
+        <v>45657</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>45596</v>
+        <v>45689</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1">
-        <v>45596</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>45747</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>45626</v>
+        <v>45747</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1">
-        <v>45626</v>
+        <v>45748</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="4">
-        <v>45657</v>
+        <v>3</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45748</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1">
-        <v>45657</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C11" s="1">
-        <v>45657</v>
+        <v>45748</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1">
-        <v>45689</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1">
-        <v>45747</v>
-      </c>
-      <c r="D13" t="s">
-        <v>36</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1">
-        <v>45747</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>3</v>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C15" s="1">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>45748</v>
+        <v>45778</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="1">
-        <v>45748</v>
-      </c>
-      <c r="D17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>39</v>
+        <v>18</v>
+      </c>
+      <c r="C17" s="4">
+        <v>45799</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1">
-        <v>45748</v>
+        <v>45809</v>
+      </c>
+      <c r="D18" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1">
-        <v>45748</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
-        <v>10</v>
+      <c r="B20" t="s">
+        <v>26</v>
       </c>
       <c r="C20" s="1">
-        <v>45778</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="D21" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1">
-        <v>45838</v>
+        <v>45900</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1">
-        <v>45838</v>
-      </c>
+        <v>45961</v>
+      </c>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1">
-        <v>45839</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="C25" s="1">
+        <v>45961</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46022</v>
       </c>
     </row>
   </sheetData>
@@ -765,7 +755,7 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E17" r:id="rId1" xr:uid="{16634FF5-BB58-4C5E-8512-A7A665D7C792}"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{16634FF5-BB58-4C5E-8512-A7A665D7C792}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
